--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>Verticals</t>
   </si>
@@ -46,67 +46,37 @@
     <t>SEBI</t>
   </si>
   <si>
-    <t>Informal Guidance</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>Request for Informal Guidance by way of an interpretative letter under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Punjab National Bank seeking interpretation of the provisions of Regulation 27 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 and SEBI Circular for implementation of recommendations of the Expert Committee for facilitating ease of doing business for listed entities dated 31.12.2024</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/commondocs/feb-2026/PNB%20-%20Informal%20Guidance%20Letter%20by%20SEBI_p.pdf</t>
-  </si>
-  <si>
-    <t>Request_for_Informal_Guidance_by_way_of_an_interpretative_letter_under_the_Secur_948a270a.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/February/Request_for_Informal_Guidance_by_way_of_an_interpretative_letter_under_the_Secur_948a270a.pdf</t>
-  </si>
-  <si>
-    <t>Listed Companies</t>
-  </si>
-  <si>
-    <t>Circular-BSE</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>Update on single filing system through API-based integration between Stock Exchanges</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/markets/MarketInfo/DispNewNoticesCirculars?page=20260220-44</t>
-  </si>
-  <si>
-    <t>Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_40202074.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/February/Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_40202074.pdf</t>
-  </si>
-  <si>
-    <t>Circular-NSE</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>Ease of doing business - mechanism for lock-in of pledged shares under SEBI (Issue of Capital and Disclosure Requirements) Regulations, 2018</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com//web/circular/2026-04/Ease_of_doing_business_mechanism_for_lock-in_of_pledged_shares_under_SEBI_Issue_of_Capital_and_Disclosure_Requirements_Regulations_2018_20260410123152.pdf</t>
-  </si>
-  <si>
-    <t>Ease_of_doing_business_mechanism_for_lock_in_of_pledged_shares_under_SEBI_Issue_8c96f01f.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/April/Ease_of_doing_business_mechanism_for_lock_in_of_pledged_shares_under_SEBI_Issue_8c96f01f.pdf</t>
+    <t>Regulations</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777351317428.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) (Amendment) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1769600297568.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
   </si>
   <si>
     <t/>
@@ -117,7 +87,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +99,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -182,28 +158,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,15 +498,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="82.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="82.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -528,7 +516,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -551,178 +539,122 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>2026</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
+      <c r="A4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Verticals</t>
   </si>
@@ -46,40 +46,25 @@
     <t>SEBI</t>
   </si>
   <si>
-    <t>Regulations</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777351317428.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) (Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1769600297568.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
-  </si>
-  <si>
-    <t/>
+    <t>Informal Guidance</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>2026-02-06</t>
+  </si>
+  <si>
+    <t>Request for Informal Guidance by way of an interpretative letter under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Punjab National Bank seeking interpretation of the provisions of Regulation 27 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 and SEBI Circular for implementation of recommendations of the Expert Committee for facilitating ease of doing business for listed entities dated 31.12.2024</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/commondocs/feb-2026/PNB%20-%20Informal%20Guidance%20Letter%20by%20SEBI_p.pdf</t>
+  </si>
+  <si>
+    <t>Request_for_Informal_Guidance_by_way_of_an_interpretative_letter_under_the_Secur_948a270a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/February/Request_for_Informal_Guidance_by_way_of_an_interpretative_letter_under_the_Secur_948a270a.pdf</t>
   </si>
 </sst>
 </file>
@@ -104,7 +89,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -158,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -175,20 +160,11 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -498,15 +474,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="82.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="82.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -568,65 +544,31 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="8"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -637,7 +579,7 @@
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="8"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -648,7 +590,7 @@
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="8"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Verticals</t>
   </si>
@@ -46,25 +46,97 @@
     <t>SEBI</t>
   </si>
   <si>
-    <t>Informal Guidance</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>Request for Informal Guidance by way of an interpretative letter under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Punjab National Bank seeking interpretation of the provisions of Regulation 27 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 and SEBI Circular for implementation of recommendations of the Expert Committee for facilitating ease of doing business for listed entities dated 31.12.2024</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/commondocs/feb-2026/PNB%20-%20Informal%20Guidance%20Letter%20by%20SEBI_p.pdf</t>
-  </si>
-  <si>
-    <t>Request_for_Informal_Guidance_by_way_of_an_interpretative_letter_under_the_Secur_948a270a.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/February/Request_for_Informal_Guidance_by_way_of_an_interpretative_letter_under_the_Secur_948a270a.pdf</t>
+    <t>Press Release</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>SEBI operationalises Past Risk and Return Verification Agency (“PaRRVA”)</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777472194521.pdf</t>
+  </si>
+  <si>
+    <t>SEBI_operationalises_Past_Risk_and_Return_Verification_Agency_PaRRVA_9f11efb2.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/SEBI_operationalises_Past_Risk_and_Return_Verification_Agency_PaRRVA_9f11efb2.pdf</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>SEBI celebrates its 38th Foundation Day</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777116554349.pdf</t>
+  </si>
+  <si>
+    <t>SEBI_celebrates_its_38th_Foundation_Day_aaf0859c.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/SEBI_celebrates_its_38th_Foundation_Day_aaf0859c.pdf</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (SEBI) signed a Memorandum of Understanding with Financial Intelligence Unit India (FIU-India)</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776340182711.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_e0467cdb.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_e0467cdb.pdf</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (SEBI) signed a Memorandum of Understanding with Department of Telecommunications (DOT), Government of India</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776256038511.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_3fea22f7.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_3fea22f7.pdf</t>
+  </si>
+  <si>
+    <t>Shri K.V.R. Murty takes charge as Whole Time Member, SEBI</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776251258103.pdf</t>
+  </si>
+  <si>
+    <t>Shri_K_V_R_Murty_takes_charge_as_Whole_Time_Member_SEBI_72c04e17.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Shri_K_V_R_Murty_takes_charge_as_Whole_Time_Member_SEBI_72c04e17.pdf</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Launch of various IT platforms by Chairman, SEBI to improve ease-of-doing business</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1775836325260.pdf</t>
+  </si>
+  <si>
+    <t>Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
   </si>
 </sst>
 </file>
@@ -72,7 +144,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +156,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -143,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -157,7 +235,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -474,15 +558,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="82.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="82.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -514,7 +598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -543,60 +627,150 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,100 +43,55 @@
     <t>Path</t>
   </si>
   <si>
-    <t>SEBI</t>
-  </si>
-  <si>
-    <t>Press Release</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>SEBI operationalises Past Risk and Return Verification Agency (“PaRRVA”)</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777472194521.pdf</t>
-  </si>
-  <si>
-    <t>SEBI_operationalises_Past_Risk_and_Return_Verification_Agency_PaRRVA_9f11efb2.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/SEBI_operationalises_Past_Risk_and_Return_Verification_Agency_PaRRVA_9f11efb2.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>SEBI celebrates its 38th Foundation Day</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1777116554349.pdf</t>
-  </si>
-  <si>
-    <t>SEBI_celebrates_its_38th_Foundation_Day_aaf0859c.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/SEBI_celebrates_its_38th_Foundation_Day_aaf0859c.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (SEBI) signed a Memorandum of Understanding with Financial Intelligence Unit India (FIU-India)</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776340182711.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_e0467cdb.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_e0467cdb.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (SEBI) signed a Memorandum of Understanding with Department of Telecommunications (DOT), Government of India</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776256038511.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_3fea22f7.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Securities_and_Exchange_Board_of_India_SEBI_signed_a_Memorandum_of_Understanding_3fea22f7.pdf</t>
-  </si>
-  <si>
-    <t>Shri K.V.R. Murty takes charge as Whole Time Member, SEBI</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776251258103.pdf</t>
-  </si>
-  <si>
-    <t>Shri_K_V_R_Murty_takes_charge_as_Whole_Time_Member_SEBI_72c04e17.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Shri_K_V_R_Murty_takes_charge_as_Whole_Time_Member_SEBI_72c04e17.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>Launch of various IT platforms by Chairman, SEBI to improve ease-of-doing business</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1775836325260.pdf</t>
-  </si>
-  <si>
-    <t>Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
+    <t>Listed Companies</t>
+  </si>
+  <si>
+    <t>Circular-BSE</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>XBRL based filing for Violations related to Code of Conduct (CoC) under SEBI PIT Regulations, 2015</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260504-17/20260504-17.pdf</t>
+  </si>
+  <si>
+    <t>XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_PIT_R_47394cc5.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_PIT_R_47394cc5.pdf</t>
+  </si>
+  <si>
+    <t>Circular-NSE</t>
+  </si>
+  <si>
+    <t>XBRL based filing for Violations related to Code of Conduct (CoC) under SEBI (Prohibition of Insider Trading) Regulations, 2015</t>
+  </si>
+  <si>
+    <t>https://nsearchives.nseindia.com//web/circular/2026-05/Violation_of_Code_of_Conduct_20260504201244.pdf</t>
+  </si>
+  <si>
+    <t>XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_Prohi_21805baa.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/May/XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_Prohi_21805baa.pdf</t>
+  </si>
+  <si>
+    <t>Filing of disclosures in XBRL format under Regulation 7(2) and Regulation 7(3) of SEBI (Prohibition of Insider Trading) Regulations, 2015</t>
+  </si>
+  <si>
+    <t>https://nsearchives.nseindia.com//web/circular/2026-05/Prohibition_of_Insider_Trading_20260504195923.pdf</t>
+  </si>
+  <si>
+    <t>Filing_of_disclosures_in_XBRL_format_under_Regulation_7_2_and_Regulation_7_3_of_9567ee38.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/May/Filing_of_disclosures_in_XBRL_format_under_Regulation_7_2_and_Regulation_7_3_of_9567ee38.pdf</t>
   </si>
 </sst>
 </file>
@@ -144,7 +99,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,12 +111,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -221,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -238,10 +187,7 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -555,18 +501,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="82.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="82.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -598,7 +544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -627,12 +573,12 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4">
         <v>2026</v>
@@ -641,7 +587,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>18</v>
@@ -661,116 +607,205 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4">
         <v>2026</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,55 +43,40 @@
     <t>Path</t>
   </si>
   <si>
-    <t>Listed Companies</t>
-  </si>
-  <si>
-    <t>Circular-BSE</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>XBRL based filing for Violations related to Code of Conduct (CoC) under SEBI PIT Regulations, 2015</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260504-17/20260504-17.pdf</t>
-  </si>
-  <si>
-    <t>XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_PIT_R_47394cc5.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_PIT_R_47394cc5.pdf</t>
-  </si>
-  <si>
-    <t>Circular-NSE</t>
-  </si>
-  <si>
-    <t>XBRL based filing for Violations related to Code of Conduct (CoC) under SEBI (Prohibition of Insider Trading) Regulations, 2015</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com//web/circular/2026-05/Violation_of_Code_of_Conduct_20260504201244.pdf</t>
-  </si>
-  <si>
-    <t>XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_Prohi_21805baa.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/May/XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_Prohi_21805baa.pdf</t>
-  </si>
-  <si>
-    <t>Filing of disclosures in XBRL format under Regulation 7(2) and Regulation 7(3) of SEBI (Prohibition of Insider Trading) Regulations, 2015</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com//web/circular/2026-05/Prohibition_of_Insider_Trading_20260504195923.pdf</t>
-  </si>
-  <si>
-    <t>Filing_of_disclosures_in_XBRL_format_under_Regulation_7_2_and_Regulation_7_3_of_9567ee38.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/May/Filing_of_disclosures_in_XBRL_format_under_Regulation_7_2_and_Regulation_7_3_of_9567ee38.pdf</t>
+    <t>SEBI</t>
+  </si>
+  <si>
+    <t>Regulations</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
+  </si>
+  <si>
+    <t>file:///Users/admin/Downloads/1780915347745.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
+  </si>
+  <si>
+    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) (Amendment) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1769600297568.pdf</t>
+  </si>
+  <si>
+    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
   </si>
 </sst>
 </file>
@@ -509,7 +494,7 @@
     <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="82.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="105.7192857142857" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -578,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>2026</v>
@@ -590,46 +575,28 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3"/>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>Verticals</t>
   </si>
@@ -46,37 +46,28 @@
     <t>SEBI</t>
   </si>
   <si>
-    <t>Regulations</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 [Last amended on January 22, 2026]</t>
-  </si>
-  <si>
-    <t>file:///Users/admin/Downloads/1780915347745.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_500e67fd.pdf</t>
-  </si>
-  <si>
-    <t>Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) (Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jan-2026/1769600297568.pdf</t>
-  </si>
-  <si>
-    <t>Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/January/Securities_and_Exchange_Board_of_India_Listing_Obligations_and_Disclosure_Requir_d9dfa16a.pdf</t>
+    <t>Press Release</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Launch of various IT platforms by Chairman, SEBI to improve ease-of-doing business</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1775836325260.pdf</t>
+  </si>
+  <si>
+    <t>Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -155,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -170,6 +161,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -489,15 +486,15 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="105.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="105.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -559,32 +556,30 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
+      <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -616,7 +611,7 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="6"/>
+      <c r="G6" s="8"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
@@ -627,7 +622,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="6"/>
+      <c r="G7" s="8"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
@@ -759,7 +754,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="6"/>
+      <c r="G19" s="8"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
@@ -770,7 +765,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="6"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="103">
   <si>
     <t>Verticals</t>
   </si>
@@ -46,28 +46,283 @@
     <t>SEBI</t>
   </si>
   <si>
+    <t>Circulars</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>Extension of timelines with repect to compliance of Digital Accessibility Circulars.</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1785493077212.pdf</t>
+  </si>
+  <si>
+    <t>Extension_of_timelines_with_repect_to_compliance_of_Digital_Accessibility_Circul_755945fb.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Extension_of_timelines_with_repect_to_compliance_of_Digital_Accessibility_Circul_755945fb.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>Ease of Doing Investment and Ease of Doing Business – Simplification and standardisation of the framework for transmission of securities</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784869499027.pdf</t>
+  </si>
+  <si>
+    <t>Ease_of_Doing_Investment_and_Ease_of_Doing_Business_Simplification_and_standardi_b54f6231.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Ease_of_Doing_Investment_and_Ease_of_Doing_Business_Simplification_and_standardi_b54f6231.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>Certification Requirements for Distribution of Specialized Investment Funds (SIFs)</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784633350069.pdf</t>
+  </si>
+  <si>
+    <t>Certification_Requirements_for_Distribution_of_Specialized_Investment_Funds_SIFs_83234fee.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Certification_Requirements_for_Distribution_of_Specialized_Investment_Funds_SIFs_83234fee.pdf</t>
+  </si>
+  <si>
+    <t>Operationalisation of freezing of holdings of promoter and promoter group including their associates (promoter holdings) at the ISIN level under Regulation 24(i)(ea) of the SEBI (Buy-back of Securities) Regulations, 2018 dated July 21, 2026</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784632576164.pdf</t>
+  </si>
+  <si>
+    <t>Operationalisation_of_freezing_of_holdings_of_promoter_and_promoter_group_includ_58c0a76f.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Operationalisation_of_freezing_of_holdings_of_promoter_and_promoter_group_includ_58c0a76f.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>Review of norms for utilization of interest or income from IPF of the Depositories</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1783423471963.pdf</t>
+  </si>
+  <si>
+    <t>Review_of_norms_for_utilization_of_interest_or_income_from_IPF_of_the_Depositori_c8f94fd5.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Review_of_norms_for_utilization_of_interest_or_income_from_IPF_of_the_Depositori_c8f94fd5.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>Handling of Client’s Unpaid Securities by Trading Members</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1783077132079.pdf</t>
+  </si>
+  <si>
+    <t>Handling_of_Clients_Unpaid_Securities_by_Trading_Members_f8a6cf7e.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Handling_of_Clients_Unpaid_Securities_by_Trading_Members_f8a6cf7e.pdf</t>
+  </si>
+  <si>
     <t>Press Release</t>
   </si>
   <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>Launch of various IT platforms by Chairman, SEBI to improve ease-of-doing business</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1775836325260.pdf</t>
-  </si>
-  <si>
-    <t>Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/April/Launch_of_various_IT_platforms_by_Chairman_SEBI_to_improve_ease_of_doing_busines_5b03b834.pdf</t>
-  </si>
-  <si>
-    <t/>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>Caution to Regulated entities and listed companies- Boss Scam</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784288188963.pdf</t>
+  </si>
+  <si>
+    <t>Caution_to_Regulated_entities_and_listed_companies_Boss_Scam_2ad13d10.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/July/Caution_to_Regulated_entities_and_listed_companies_Boss_Scam_2ad13d10.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>SEBI Launches Two New Investor Awareness Videos to Promote Corporate Bond Market Awareness</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1783615648681.pdf</t>
+  </si>
+  <si>
+    <t>SEBI_Launches_Two_New_Investor_Awareness_Videos_to_Promote_Corporate_Bond_Market_4dc1d03a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/July/SEBI_Launches_Two_New_Investor_Awareness_Videos_to_Promote_Corporate_Bond_Market_4dc1d03a.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>SETTLEMENT HELPDESK FACILITY</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1782919901643.pdf</t>
+  </si>
+  <si>
+    <t>SETTLEMENT_HELPDESK_FACILITY_3a4f5700.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/July/SETTLEMENT_HELPDESK_FACILITY_3a4f5700.pdf</t>
+  </si>
+  <si>
+    <t>Consultation Paper</t>
+  </si>
+  <si>
+    <t>Consultation Paper on Streamlining the Online Dispute Resolution Framework in Indian Securities Market</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784805207495.pdf</t>
+  </si>
+  <si>
+    <t>Consultation_Paper_on_Streamlining_the_Online_Dispute_Resolution_Framework_in_In_8fa0cbcd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Consultation Paper/2026/July/Consultation_Paper_on_Streamlining_the_Online_Dispute_Resolution_Framework_in_In_8fa0cbcd.pdf</t>
+  </si>
+  <si>
+    <t>Consultation Paper on Comprehensive Review of SEBI (Portfolio Managers) Regulations, 2020</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784803038906.pdf</t>
+  </si>
+  <si>
+    <t>Consultation_Paper_on_Comprehensive_Review_of_SEBI_Portfolio_Managers_Regulation_762edca1.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Consultation Paper/2026/July/Consultation_Paper_on_Comprehensive_Review_of_SEBI_Portfolio_Managers_Regulation_762edca1.pdf</t>
+  </si>
+  <si>
+    <t>Master Circular</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>Master Circular for Merchant Bankers</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784029390357.pdf</t>
+  </si>
+  <si>
+    <t>Master_Circular_for_Merchant_Bankers_ea33b8c1.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Master Circular/2026/July/Master_Circular_for_Merchant_Bankers_ea33b8c1.pdf</t>
+  </si>
+  <si>
+    <t>Informal Guidance</t>
+  </si>
+  <si>
+    <t>Request for Informal Guidance under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from IDBI Bank Limited in relation to sale of equity shares of various unlisted companies held by IDBI Bank Limited to non-QIB investors</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/commondocs/jul-2026/Informal%20Guidance%20Letter%20by%20SEBI%2031.07.26_p.pdf</t>
+  </si>
+  <si>
+    <t>Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_c052b5cf.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/July/Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_c052b5cf.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>Request for Informal Guidance under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Ananya Finance for Inclusive Growth Private Limited in relation to Regulation 62A of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/commondocs/jul-2026/Informal%20Guidance%20Letter%20by%20SEBI%20-%20SEBI_p.pdf</t>
+  </si>
+  <si>
+    <t>Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_7367562d.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/July/Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_7367562d.pdf</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>Request for Informal Guidance under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Sundaram Alternate Assets Limited in relation to Regulation 24(3A) of the Securities and Exchange Board of India (Portfolio Managers) Regulations, 2020 read with paragraph 3.4 of the Master Circular for Portfolio Managers dated July 16, 2025</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/commondocs/jul-2026/Informal%20Guidance_p.pdf</t>
+  </si>
+  <si>
+    <t>Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_96b65ef4.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/July/Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_96b65ef4.pdf</t>
+  </si>
+  <si>
+    <t>Listed Companies</t>
+  </si>
+  <si>
+    <t>Circular-BSE</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>SEBI (Listing Obligations and Disclosure Requirements) (Second Amendment) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260722-7/20260722-7.pdf</t>
+  </si>
+  <si>
+    <t>SEBI_Listing_Obligations_and_Disclosure_Requirements_Second_Amendment_Regulation_99825bce.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/July/SEBI_Listing_Obligations_and_Disclosure_Requirements_Second_Amendment_Regulation_99825bce.pdf</t>
+  </si>
+  <si>
+    <t>Circular-NSE</t>
+  </si>
+  <si>
+    <t>FAQs on Filing of Corporate Action as per SEBI (LODR) Regulations, 2015</t>
+  </si>
+  <si>
+    <t>https://nsearchives.nseindia.com//web/circular/2026-07/FAQs_on_Corporate_Action_20260708204832.pdf</t>
+  </si>
+  <si>
+    <t>FAQs_on_Filing_of_Corporate_Action_as_per_SEBI_LODR_Regulations_2015_ce15c015.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/July/FAQs_on_Filing_of_Corporate_Action_as_per_SEBI_LODR_Regulations_2015_ce15c015.pdf</t>
+  </si>
+  <si>
+    <t>Norms for Base Price, Price Bands, Call Auction in pre-open session and Close-out procedure for Exchange Traded Funds (ETFs)</t>
+  </si>
+  <si>
+    <t>https://nsearchives.nseindia.com//web/circular/2026-07/NSE_Circular_20260703192238.pdf</t>
+  </si>
+  <si>
+    <t>Norms_for_Base_Price_Price_Bands_Call_Auction_in_pre_open_session_and_Close_out_149eb5e1.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/July/Norms_for_Base_Price_Price_Bands_Call_Auction_in_pre_open_session_and_Close_out_149eb5e1.pdf</t>
   </si>
 </sst>
 </file>
@@ -146,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -161,12 +416,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -486,15 +735,15 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="105.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="105.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -556,207 +805,497 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="6" t="s">
+      <c r="F11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3"/>
@@ -765,7 +1304,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="8"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="10">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,286 +43,7 @@
     <t>Path</t>
   </si>
   <si>
-    <t>SEBI</t>
-  </si>
-  <si>
-    <t>Circulars</t>
-  </si>
-  <si>
-    <t>July</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>Extension of timelines with repect to compliance of Digital Accessibility Circulars.</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1785493077212.pdf</t>
-  </si>
-  <si>
-    <t>Extension_of_timelines_with_repect_to_compliance_of_Digital_Accessibility_Circul_755945fb.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Extension_of_timelines_with_repect_to_compliance_of_Digital_Accessibility_Circul_755945fb.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>Ease of Doing Investment and Ease of Doing Business – Simplification and standardisation of the framework for transmission of securities</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784869499027.pdf</t>
-  </si>
-  <si>
-    <t>Ease_of_Doing_Investment_and_Ease_of_Doing_Business_Simplification_and_standardi_b54f6231.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Ease_of_Doing_Investment_and_Ease_of_Doing_Business_Simplification_and_standardi_b54f6231.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>Certification Requirements for Distribution of Specialized Investment Funds (SIFs)</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784633350069.pdf</t>
-  </si>
-  <si>
-    <t>Certification_Requirements_for_Distribution_of_Specialized_Investment_Funds_SIFs_83234fee.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Certification_Requirements_for_Distribution_of_Specialized_Investment_Funds_SIFs_83234fee.pdf</t>
-  </si>
-  <si>
-    <t>Operationalisation of freezing of holdings of promoter and promoter group including their associates (promoter holdings) at the ISIN level under Regulation 24(i)(ea) of the SEBI (Buy-back of Securities) Regulations, 2018 dated July 21, 2026</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784632576164.pdf</t>
-  </si>
-  <si>
-    <t>Operationalisation_of_freezing_of_holdings_of_promoter_and_promoter_group_includ_58c0a76f.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Operationalisation_of_freezing_of_holdings_of_promoter_and_promoter_group_includ_58c0a76f.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>Review of norms for utilization of interest or income from IPF of the Depositories</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1783423471963.pdf</t>
-  </si>
-  <si>
-    <t>Review_of_norms_for_utilization_of_interest_or_income_from_IPF_of_the_Depositori_c8f94fd5.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Review_of_norms_for_utilization_of_interest_or_income_from_IPF_of_the_Depositori_c8f94fd5.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>Handling of Client’s Unpaid Securities by Trading Members</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1783077132079.pdf</t>
-  </si>
-  <si>
-    <t>Handling_of_Clients_Unpaid_Securities_by_Trading_Members_f8a6cf7e.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/July/Handling_of_Clients_Unpaid_Securities_by_Trading_Members_f8a6cf7e.pdf</t>
-  </si>
-  <si>
-    <t>Press Release</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>Caution to Regulated entities and listed companies- Boss Scam</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784288188963.pdf</t>
-  </si>
-  <si>
-    <t>Caution_to_Regulated_entities_and_listed_companies_Boss_Scam_2ad13d10.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/July/Caution_to_Regulated_entities_and_listed_companies_Boss_Scam_2ad13d10.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>SEBI Launches Two New Investor Awareness Videos to Promote Corporate Bond Market Awareness</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1783615648681.pdf</t>
-  </si>
-  <si>
-    <t>SEBI_Launches_Two_New_Investor_Awareness_Videos_to_Promote_Corporate_Bond_Market_4dc1d03a.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/July/SEBI_Launches_Two_New_Investor_Awareness_Videos_to_Promote_Corporate_Bond_Market_4dc1d03a.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>SETTLEMENT HELPDESK FACILITY</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1782919901643.pdf</t>
-  </si>
-  <si>
-    <t>SETTLEMENT_HELPDESK_FACILITY_3a4f5700.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/July/SETTLEMENT_HELPDESK_FACILITY_3a4f5700.pdf</t>
-  </si>
-  <si>
-    <t>Consultation Paper</t>
-  </si>
-  <si>
-    <t>Consultation Paper on Streamlining the Online Dispute Resolution Framework in Indian Securities Market</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784805207495.pdf</t>
-  </si>
-  <si>
-    <t>Consultation_Paper_on_Streamlining_the_Online_Dispute_Resolution_Framework_in_In_8fa0cbcd.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Consultation Paper/2026/July/Consultation_Paper_on_Streamlining_the_Online_Dispute_Resolution_Framework_in_In_8fa0cbcd.pdf</t>
-  </si>
-  <si>
-    <t>Consultation Paper on Comprehensive Review of SEBI (Portfolio Managers) Regulations, 2020</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784803038906.pdf</t>
-  </si>
-  <si>
-    <t>Consultation_Paper_on_Comprehensive_Review_of_SEBI_Portfolio_Managers_Regulation_762edca1.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Consultation Paper/2026/July/Consultation_Paper_on_Comprehensive_Review_of_SEBI_Portfolio_Managers_Regulation_762edca1.pdf</t>
-  </si>
-  <si>
-    <t>Master Circular</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>Master Circular for Merchant Bankers</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/attachdocs/jul-2026/1784029390357.pdf</t>
-  </si>
-  <si>
-    <t>Master_Circular_for_Merchant_Bankers_ea33b8c1.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Master Circular/2026/July/Master_Circular_for_Merchant_Bankers_ea33b8c1.pdf</t>
-  </si>
-  <si>
-    <t>Informal Guidance</t>
-  </si>
-  <si>
-    <t>Request for Informal Guidance under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from IDBI Bank Limited in relation to sale of equity shares of various unlisted companies held by IDBI Bank Limited to non-QIB investors</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/commondocs/jul-2026/Informal%20Guidance%20Letter%20by%20SEBI%2031.07.26_p.pdf</t>
-  </si>
-  <si>
-    <t>Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_c052b5cf.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/July/Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_c052b5cf.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>Request for Informal Guidance under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Ananya Finance for Inclusive Growth Private Limited in relation to Regulation 62A of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/commondocs/jul-2026/Informal%20Guidance%20Letter%20by%20SEBI%20-%20SEBI_p.pdf</t>
-  </si>
-  <si>
-    <t>Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_7367562d.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/July/Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_7367562d.pdf</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>Request for Informal Guidance under the Securities and Exchange Board of India (Informal Guidance) Scheme, 2025 received from Sundaram Alternate Assets Limited in relation to Regulation 24(3A) of the Securities and Exchange Board of India (Portfolio Managers) Regulations, 2020 read with paragraph 3.4 of the Master Circular for Portfolio Managers dated July 16, 2025</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/commondocs/jul-2026/Informal%20Guidance_p.pdf</t>
-  </si>
-  <si>
-    <t>Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_96b65ef4.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Informal Guidance/2026/July/Request_for_Informal_Guidance_under_the_Securities_and_Exchange_Board_of_India_I_96b65ef4.pdf</t>
-  </si>
-  <si>
-    <t>Listed Companies</t>
-  </si>
-  <si>
-    <t>Circular-BSE</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>SEBI (Listing Obligations and Disclosure Requirements) (Second Amendment) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260722-7/20260722-7.pdf</t>
-  </si>
-  <si>
-    <t>SEBI_Listing_Obligations_and_Disclosure_Requirements_Second_Amendment_Regulation_99825bce.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/July/SEBI_Listing_Obligations_and_Disclosure_Requirements_Second_Amendment_Regulation_99825bce.pdf</t>
-  </si>
-  <si>
-    <t>Circular-NSE</t>
-  </si>
-  <si>
-    <t>FAQs on Filing of Corporate Action as per SEBI (LODR) Regulations, 2015</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com//web/circular/2026-07/FAQs_on_Corporate_Action_20260708204832.pdf</t>
-  </si>
-  <si>
-    <t>FAQs_on_Filing_of_Corporate_Action_as_per_SEBI_LODR_Regulations_2015_ce15c015.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/July/FAQs_on_Filing_of_Corporate_Action_as_per_SEBI_LODR_Regulations_2015_ce15c015.pdf</t>
-  </si>
-  <si>
-    <t>Norms for Base Price, Price Bands, Call Auction in pre-open session and Close-out procedure for Exchange Traded Funds (ETFs)</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com//web/circular/2026-07/NSE_Circular_20260703192238.pdf</t>
-  </si>
-  <si>
-    <t>Norms_for_Base_Price_Price_Bands_Call_Auction_in_pre_open_session_and_Close_out_149eb5e1.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-NSE/2026/July/Norms_for_Base_Price_Price_Bands_Call_Auction_in_pre_open_session_and_Close_out_149eb5e1.pdf</t>
+    <t/>
   </si>
 </sst>
 </file>
@@ -409,16 +130,16 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -732,7 +453,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -740,7 +461,7 @@
     <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="105.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="125.57642857142856" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -780,28 +501,26 @@
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -809,28 +528,26 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -838,28 +555,26 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -867,28 +582,26 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -896,28 +609,26 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -925,28 +636,26 @@
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -954,28 +663,26 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -983,28 +690,26 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -1012,28 +717,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -1041,28 +744,26 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -1070,28 +771,26 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -1099,57 +798,53 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -1157,28 +852,26 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C15" s="4"/>
       <c r="D15" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
@@ -1186,127 +879,162 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2026</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Pravartiya/data/test.xlsx
+++ b/Pravartiya/data/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="10">
   <si>
     <t>Verticals</t>
   </si>
@@ -51,7 +51,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,12 +68,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -122,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -136,10 +142,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -453,18 +462,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="125.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -621,7 +630,7 @@
       <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -648,7 +657,7 @@
       <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -820,7 +829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
@@ -999,7 +1008,7 @@
       <c r="F20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="3" t="s">
@@ -1026,13 +1035,337 @@
       <c r="F21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+      <c r="A24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+      <c r="A25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+      <c r="A26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+      <c r="A27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+      <c r="A29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+      <c r="A33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>9</v>
       </c>
     </row>
